--- a/bds/Biblioteca.xlsx
+++ b/bds/Biblioteca.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\CODE\hermesfar\bds\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0EEC001E-5818-4985-BF6F-82A1E25D0987}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00356564-56F4-4224-A0B9-751F9ED55F8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/bds/Biblioteca.xlsx
+++ b/bds/Biblioteca.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\CODE\hermesfar\bds\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00356564-56F4-4224-A0B9-751F9ED55F8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C08B1E93-B92D-4EFA-B886-087168ABC4B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5038" uniqueCount="1230">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5047" uniqueCount="1232">
   <si>
     <t>ID</t>
   </si>
@@ -3723,6 +3723,12 @@
   </si>
   <si>
     <t>El loco en el fin del mundo</t>
+  </si>
+  <si>
+    <t>Tres novelas exóticas</t>
+  </si>
+  <si>
+    <t>Rey Rosa, R.</t>
   </si>
 </sst>
 </file>
@@ -4123,7 +4129,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K558"/>
+  <dimension ref="A1:K559"/>
   <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="6.44140625" customWidth="1"/>
@@ -23662,6 +23668,41 @@
         <v>14</v>
       </c>
       <c r="K558" t="s">
+        <v>651</v>
+      </c>
+    </row>
+    <row r="559" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A559">
+        <v>558</v>
+      </c>
+      <c r="B559" t="s">
+        <v>1230</v>
+      </c>
+      <c r="C559" t="s">
+        <v>1231</v>
+      </c>
+      <c r="D559" t="s">
+        <v>43</v>
+      </c>
+      <c r="E559">
+        <v>2016</v>
+      </c>
+      <c r="F559" t="s">
+        <v>239</v>
+      </c>
+      <c r="G559" t="s">
+        <v>651</v>
+      </c>
+      <c r="H559" t="s">
+        <v>651</v>
+      </c>
+      <c r="I559" t="s">
+        <v>14</v>
+      </c>
+      <c r="J559" t="s">
+        <v>14</v>
+      </c>
+      <c r="K559" t="s">
         <v>651</v>
       </c>
     </row>

--- a/bds/Biblioteca.xlsx
+++ b/bds/Biblioteca.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\CODE\hermesfar\bds\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C08B1E93-B92D-4EFA-B886-087168ABC4B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BED2BCE-EFE5-4B92-83EB-325927DA0941}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5047" uniqueCount="1232">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5065" uniqueCount="1235">
   <si>
     <t>ID</t>
   </si>
@@ -3729,6 +3729,15 @@
   </si>
   <si>
     <t>Rey Rosa, R.</t>
+  </si>
+  <si>
+    <t>El trimestre económico. Enero - Marzo de 2026 #369</t>
+  </si>
+  <si>
+    <t>La Isla de la Pasión</t>
+  </si>
+  <si>
+    <t>Restrepo, L.</t>
   </si>
 </sst>
 </file>
@@ -4129,7 +4138,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K559"/>
+  <dimension ref="A1:K561"/>
   <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="6.44140625" customWidth="1"/>
@@ -23557,7 +23566,7 @@
         <v>651</v>
       </c>
       <c r="I555" t="s">
-        <v>14</v>
+        <v>194</v>
       </c>
       <c r="J555" t="s">
         <v>14</v>
@@ -23592,7 +23601,7 @@
         <v>651</v>
       </c>
       <c r="I556" t="s">
-        <v>14</v>
+        <v>194</v>
       </c>
       <c r="J556" t="s">
         <v>14</v>
@@ -23703,6 +23712,76 @@
         <v>14</v>
       </c>
       <c r="K559" t="s">
+        <v>651</v>
+      </c>
+    </row>
+    <row r="560" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A560">
+        <v>559</v>
+      </c>
+      <c r="B560" t="s">
+        <v>1232</v>
+      </c>
+      <c r="C560" t="s">
+        <v>55</v>
+      </c>
+      <c r="D560" t="s">
+        <v>55</v>
+      </c>
+      <c r="E560">
+        <v>2026</v>
+      </c>
+      <c r="F560" t="s">
+        <v>239</v>
+      </c>
+      <c r="G560" t="s">
+        <v>651</v>
+      </c>
+      <c r="H560" t="s">
+        <v>651</v>
+      </c>
+      <c r="I560" t="s">
+        <v>14</v>
+      </c>
+      <c r="J560" t="s">
+        <v>14</v>
+      </c>
+      <c r="K560" t="s">
+        <v>651</v>
+      </c>
+    </row>
+    <row r="561" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A561">
+        <v>560</v>
+      </c>
+      <c r="B561" t="s">
+        <v>1233</v>
+      </c>
+      <c r="C561" t="s">
+        <v>1234</v>
+      </c>
+      <c r="D561" t="s">
+        <v>43</v>
+      </c>
+      <c r="E561">
+        <v>2015</v>
+      </c>
+      <c r="F561" t="s">
+        <v>239</v>
+      </c>
+      <c r="G561" t="s">
+        <v>651</v>
+      </c>
+      <c r="H561" t="s">
+        <v>651</v>
+      </c>
+      <c r="I561" t="s">
+        <v>14</v>
+      </c>
+      <c r="J561" t="s">
+        <v>14</v>
+      </c>
+      <c r="K561" t="s">
         <v>651</v>
       </c>
     </row>

--- a/bds/Biblioteca.xlsx
+++ b/bds/Biblioteca.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\CODE\hermesfar\bds\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BED2BCE-EFE5-4B92-83EB-325927DA0941}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CDA947D-8890-42B0-B292-B96969B0DA4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5065" uniqueCount="1235">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5101" uniqueCount="1243">
   <si>
     <t>ID</t>
   </si>
@@ -3738,6 +3738,30 @@
   </si>
   <si>
     <t>Restrepo, L.</t>
+  </si>
+  <si>
+    <t>Elogio de la educación</t>
+  </si>
+  <si>
+    <t>Vargas Llosa, M.</t>
+  </si>
+  <si>
+    <t>Civilización y barbarie</t>
+  </si>
+  <si>
+    <t>Samiento, D. F.</t>
+  </si>
+  <si>
+    <t>CONACULTA</t>
+  </si>
+  <si>
+    <t>La muerte de Tyrone Power en el Monumental del Barcelona</t>
+  </si>
+  <si>
+    <t>Donoso Pareja, M.</t>
+  </si>
+  <si>
+    <t>Nueve noches con Violeta del Río (ilustrado por Edu Molina)</t>
   </si>
 </sst>
 </file>
@@ -4138,7 +4162,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K561"/>
+  <dimension ref="A1:K565"/>
   <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="6.44140625" customWidth="1"/>
@@ -23782,6 +23806,146 @@
         <v>14</v>
       </c>
       <c r="K561" t="s">
+        <v>651</v>
+      </c>
+    </row>
+    <row r="562" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A562">
+        <v>561</v>
+      </c>
+      <c r="B562" t="s">
+        <v>1235</v>
+      </c>
+      <c r="C562" t="s">
+        <v>1236</v>
+      </c>
+      <c r="D562" t="s">
+        <v>450</v>
+      </c>
+      <c r="E562">
+        <v>2025</v>
+      </c>
+      <c r="F562" t="s">
+        <v>239</v>
+      </c>
+      <c r="G562" t="s">
+        <v>651</v>
+      </c>
+      <c r="H562" t="s">
+        <v>651</v>
+      </c>
+      <c r="I562" t="s">
+        <v>14</v>
+      </c>
+      <c r="J562" t="s">
+        <v>14</v>
+      </c>
+      <c r="K562" t="s">
+        <v>651</v>
+      </c>
+    </row>
+    <row r="563" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A563">
+        <v>562</v>
+      </c>
+      <c r="B563" t="s">
+        <v>1237</v>
+      </c>
+      <c r="C563" t="s">
+        <v>1238</v>
+      </c>
+      <c r="D563" t="s">
+        <v>1239</v>
+      </c>
+      <c r="E563">
+        <v>2013</v>
+      </c>
+      <c r="F563" t="s">
+        <v>239</v>
+      </c>
+      <c r="G563" t="s">
+        <v>651</v>
+      </c>
+      <c r="H563" t="s">
+        <v>651</v>
+      </c>
+      <c r="I563" t="s">
+        <v>14</v>
+      </c>
+      <c r="J563" t="s">
+        <v>14</v>
+      </c>
+      <c r="K563" t="s">
+        <v>651</v>
+      </c>
+    </row>
+    <row r="564" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A564">
+        <v>563</v>
+      </c>
+      <c r="B564" t="s">
+        <v>1240</v>
+      </c>
+      <c r="C564" t="s">
+        <v>1241</v>
+      </c>
+      <c r="D564" t="s">
+        <v>55</v>
+      </c>
+      <c r="E564">
+        <v>2025</v>
+      </c>
+      <c r="F564" t="s">
+        <v>239</v>
+      </c>
+      <c r="G564" t="s">
+        <v>651</v>
+      </c>
+      <c r="H564" t="s">
+        <v>651</v>
+      </c>
+      <c r="I564" t="s">
+        <v>14</v>
+      </c>
+      <c r="J564" t="s">
+        <v>14</v>
+      </c>
+      <c r="K564" t="s">
+        <v>651</v>
+      </c>
+    </row>
+    <row r="565" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A565">
+        <v>564</v>
+      </c>
+      <c r="B565" t="s">
+        <v>1242</v>
+      </c>
+      <c r="C565" t="s">
+        <v>761</v>
+      </c>
+      <c r="D565" t="s">
+        <v>55</v>
+      </c>
+      <c r="E565">
+        <v>2022</v>
+      </c>
+      <c r="F565" t="s">
+        <v>239</v>
+      </c>
+      <c r="G565" t="s">
+        <v>651</v>
+      </c>
+      <c r="H565" t="s">
+        <v>651</v>
+      </c>
+      <c r="I565" t="s">
+        <v>14</v>
+      </c>
+      <c r="J565" t="s">
+        <v>14</v>
+      </c>
+      <c r="K565" t="s">
         <v>651</v>
       </c>
     </row>

--- a/bds/Biblioteca.xlsx
+++ b/bds/Biblioteca.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\CODE\hermesfar\bds\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CDA947D-8890-42B0-B292-B96969B0DA4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C37A3A31-2C50-48C8-A1AA-D55AEFFB2A48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5101" uniqueCount="1243">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5128" uniqueCount="1249">
   <si>
     <t>ID</t>
   </si>
@@ -3762,6 +3762,24 @@
   </si>
   <si>
     <t>Nueve noches con Violeta del Río (ilustrado por Edu Molina)</t>
+  </si>
+  <si>
+    <t>Pato Babs</t>
+  </si>
+  <si>
+    <t>Men at War</t>
+  </si>
+  <si>
+    <t>Wing Books</t>
+  </si>
+  <si>
+    <t>Santa Evita</t>
+  </si>
+  <si>
+    <t>La novela de Perón</t>
+  </si>
+  <si>
+    <t>Martínez, T. E.</t>
   </si>
 </sst>
 </file>
@@ -4162,7 +4180,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K565"/>
+  <dimension ref="A1:K568"/>
   <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="6.44140625" customWidth="1"/>
@@ -22511,7 +22529,7 @@
         <v>14</v>
       </c>
       <c r="K524" t="s">
-        <v>651</v>
+        <v>1243</v>
       </c>
     </row>
     <row r="525" spans="1:11" x14ac:dyDescent="0.3">
@@ -22791,7 +22809,7 @@
         <v>14</v>
       </c>
       <c r="K532" t="s">
-        <v>651</v>
+        <v>1243</v>
       </c>
     </row>
     <row r="533" spans="1:11" x14ac:dyDescent="0.3">
@@ -23141,7 +23159,7 @@
         <v>14</v>
       </c>
       <c r="K542" t="s">
-        <v>651</v>
+        <v>1243</v>
       </c>
     </row>
     <row r="543" spans="1:11" x14ac:dyDescent="0.3">
@@ -23176,7 +23194,7 @@
         <v>14</v>
       </c>
       <c r="K543" t="s">
-        <v>651</v>
+        <v>1243</v>
       </c>
     </row>
     <row r="544" spans="1:11" x14ac:dyDescent="0.3">
@@ -23946,6 +23964,111 @@
         <v>14</v>
       </c>
       <c r="K565" t="s">
+        <v>651</v>
+      </c>
+    </row>
+    <row r="566" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A566">
+        <v>565</v>
+      </c>
+      <c r="B566" t="s">
+        <v>1244</v>
+      </c>
+      <c r="C566" t="s">
+        <v>812</v>
+      </c>
+      <c r="D566" t="s">
+        <v>1245</v>
+      </c>
+      <c r="E566">
+        <v>1991</v>
+      </c>
+      <c r="F566" t="s">
+        <v>1016</v>
+      </c>
+      <c r="G566" t="s">
+        <v>651</v>
+      </c>
+      <c r="H566" t="s">
+        <v>651</v>
+      </c>
+      <c r="I566" t="s">
+        <v>14</v>
+      </c>
+      <c r="J566" t="s">
+        <v>14</v>
+      </c>
+      <c r="K566" t="s">
+        <v>651</v>
+      </c>
+    </row>
+    <row r="567" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A567">
+        <v>566</v>
+      </c>
+      <c r="B567" t="s">
+        <v>1246</v>
+      </c>
+      <c r="C567" t="s">
+        <v>1248</v>
+      </c>
+      <c r="D567" t="s">
+        <v>72</v>
+      </c>
+      <c r="E567">
+        <v>1997</v>
+      </c>
+      <c r="F567" t="s">
+        <v>239</v>
+      </c>
+      <c r="G567" t="s">
+        <v>651</v>
+      </c>
+      <c r="H567" t="s">
+        <v>651</v>
+      </c>
+      <c r="I567" t="s">
+        <v>14</v>
+      </c>
+      <c r="J567" t="s">
+        <v>14</v>
+      </c>
+      <c r="K567" t="s">
+        <v>651</v>
+      </c>
+    </row>
+    <row r="568" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A568">
+        <v>567</v>
+      </c>
+      <c r="B568" t="s">
+        <v>1247</v>
+      </c>
+      <c r="C568" t="s">
+        <v>1248</v>
+      </c>
+      <c r="D568" t="s">
+        <v>72</v>
+      </c>
+      <c r="E568">
+        <v>1996</v>
+      </c>
+      <c r="F568" t="s">
+        <v>239</v>
+      </c>
+      <c r="G568" t="s">
+        <v>651</v>
+      </c>
+      <c r="H568" t="s">
+        <v>651</v>
+      </c>
+      <c r="I568" t="s">
+        <v>14</v>
+      </c>
+      <c r="J568" t="s">
+        <v>14</v>
+      </c>
+      <c r="K568" t="s">
         <v>651</v>
       </c>
     </row>

--- a/bds/Biblioteca.xlsx
+++ b/bds/Biblioteca.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\CODE\hermesfar\bds\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C37A3A31-2C50-48C8-A1AA-D55AEFFB2A48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02AB64E8-C8D3-493C-97E3-8AD2742AAFB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5128" uniqueCount="1249">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5137" uniqueCount="1251">
   <si>
     <t>ID</t>
   </si>
@@ -3780,6 +3780,12 @@
   </si>
   <si>
     <t>Martínez, T. E.</t>
+  </si>
+  <si>
+    <t>Todos los cuentos</t>
+  </si>
+  <si>
+    <t>Adriana Hidalgo Editora</t>
   </si>
 </sst>
 </file>
@@ -4180,7 +4186,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K568"/>
+  <dimension ref="A1:K569"/>
   <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="6.44140625" customWidth="1"/>
@@ -22138,10 +22144,10 @@
         <v>651</v>
       </c>
       <c r="I513" t="s">
-        <v>14</v>
+        <v>194</v>
       </c>
       <c r="J513" t="s">
-        <v>14</v>
+        <v>194</v>
       </c>
       <c r="K513" t="s">
         <v>651</v>
@@ -22809,7 +22815,7 @@
         <v>14</v>
       </c>
       <c r="K532" t="s">
-        <v>1243</v>
+        <v>651</v>
       </c>
     </row>
     <row r="533" spans="1:11" x14ac:dyDescent="0.3">
@@ -23194,7 +23200,7 @@
         <v>14</v>
       </c>
       <c r="K543" t="s">
-        <v>1243</v>
+        <v>651</v>
       </c>
     </row>
     <row r="544" spans="1:11" x14ac:dyDescent="0.3">
@@ -23853,10 +23859,10 @@
         <v>651</v>
       </c>
       <c r="I562" t="s">
-        <v>14</v>
+        <v>194</v>
       </c>
       <c r="J562" t="s">
-        <v>14</v>
+        <v>194</v>
       </c>
       <c r="K562" t="s">
         <v>651</v>
@@ -24069,6 +24075,41 @@
         <v>14</v>
       </c>
       <c r="K568" t="s">
+        <v>651</v>
+      </c>
+    </row>
+    <row r="569" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A569">
+        <v>568</v>
+      </c>
+      <c r="B569" t="s">
+        <v>1249</v>
+      </c>
+      <c r="C569" t="s">
+        <v>949</v>
+      </c>
+      <c r="D569" t="s">
+        <v>1250</v>
+      </c>
+      <c r="E569">
+        <v>2011</v>
+      </c>
+      <c r="F569" t="s">
+        <v>19</v>
+      </c>
+      <c r="G569" t="s">
+        <v>651</v>
+      </c>
+      <c r="H569" t="s">
+        <v>651</v>
+      </c>
+      <c r="I569" t="s">
+        <v>14</v>
+      </c>
+      <c r="J569" t="s">
+        <v>14</v>
+      </c>
+      <c r="K569" t="s">
         <v>651</v>
       </c>
     </row>

--- a/bds/Biblioteca.xlsx
+++ b/bds/Biblioteca.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\CODE\hermesfar\bds\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02AB64E8-C8D3-493C-97E3-8AD2742AAFB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3BC57CDC-455F-4CC9-B8AE-E68ED1E732F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23509,10 +23509,10 @@
         <v>651</v>
       </c>
       <c r="I552" t="s">
-        <v>14</v>
+        <v>194</v>
       </c>
       <c r="J552" t="s">
-        <v>14</v>
+        <v>194</v>
       </c>
       <c r="K552" t="s">
         <v>651</v>

--- a/bds/Biblioteca.xlsx
+++ b/bds/Biblioteca.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\CODE\hermesfar\bds\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3BC57CDC-455F-4CC9-B8AE-E68ED1E732F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49DE6F2A-DAA8-423C-AEC3-67F4C29D8A90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3722,9 +3722,6 @@
     <t>El evangelio según Jesucristo</t>
   </si>
   <si>
-    <t>El loco en el fin del mundo</t>
-  </si>
-  <si>
     <t>Tres novelas exóticas</t>
   </si>
   <si>
@@ -3786,6 +3783,9 @@
   </si>
   <si>
     <t>Adriana Hidalgo Editora</t>
+  </si>
+  <si>
+    <t>El loco de Dios en el fin del mundo</t>
   </si>
 </sst>
 </file>
@@ -22535,7 +22535,7 @@
         <v>14</v>
       </c>
       <c r="K524" t="s">
-        <v>1243</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="525" spans="1:11" x14ac:dyDescent="0.3">
@@ -23165,7 +23165,7 @@
         <v>14</v>
       </c>
       <c r="K542" t="s">
-        <v>1243</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="543" spans="1:11" x14ac:dyDescent="0.3">
@@ -23698,7 +23698,7 @@
         <v>557</v>
       </c>
       <c r="B558" t="s">
-        <v>1229</v>
+        <v>1250</v>
       </c>
       <c r="C558" t="s">
         <v>1161</v>
@@ -23719,7 +23719,7 @@
         <v>651</v>
       </c>
       <c r="I558" t="s">
-        <v>14</v>
+        <v>194</v>
       </c>
       <c r="J558" t="s">
         <v>14</v>
@@ -23733,10 +23733,10 @@
         <v>558</v>
       </c>
       <c r="B559" t="s">
+        <v>1229</v>
+      </c>
+      <c r="C559" t="s">
         <v>1230</v>
-      </c>
-      <c r="C559" t="s">
-        <v>1231</v>
       </c>
       <c r="D559" t="s">
         <v>43</v>
@@ -23768,7 +23768,7 @@
         <v>559</v>
       </c>
       <c r="B560" t="s">
-        <v>1232</v>
+        <v>1231</v>
       </c>
       <c r="C560" t="s">
         <v>55</v>
@@ -23803,10 +23803,10 @@
         <v>560</v>
       </c>
       <c r="B561" t="s">
+        <v>1232</v>
+      </c>
+      <c r="C561" t="s">
         <v>1233</v>
-      </c>
-      <c r="C561" t="s">
-        <v>1234</v>
       </c>
       <c r="D561" t="s">
         <v>43</v>
@@ -23838,10 +23838,10 @@
         <v>561</v>
       </c>
       <c r="B562" t="s">
+        <v>1234</v>
+      </c>
+      <c r="C562" t="s">
         <v>1235</v>
-      </c>
-      <c r="C562" t="s">
-        <v>1236</v>
       </c>
       <c r="D562" t="s">
         <v>450</v>
@@ -23873,13 +23873,13 @@
         <v>562</v>
       </c>
       <c r="B563" t="s">
+        <v>1236</v>
+      </c>
+      <c r="C563" t="s">
         <v>1237</v>
       </c>
-      <c r="C563" t="s">
+      <c r="D563" t="s">
         <v>1238</v>
-      </c>
-      <c r="D563" t="s">
-        <v>1239</v>
       </c>
       <c r="E563">
         <v>2013</v>
@@ -23908,10 +23908,10 @@
         <v>563</v>
       </c>
       <c r="B564" t="s">
+        <v>1239</v>
+      </c>
+      <c r="C564" t="s">
         <v>1240</v>
-      </c>
-      <c r="C564" t="s">
-        <v>1241</v>
       </c>
       <c r="D564" t="s">
         <v>55</v>
@@ -23943,7 +23943,7 @@
         <v>564</v>
       </c>
       <c r="B565" t="s">
-        <v>1242</v>
+        <v>1241</v>
       </c>
       <c r="C565" t="s">
         <v>761</v>
@@ -23978,13 +23978,13 @@
         <v>565</v>
       </c>
       <c r="B566" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="C566" t="s">
         <v>812</v>
       </c>
       <c r="D566" t="s">
-        <v>1245</v>
+        <v>1244</v>
       </c>
       <c r="E566">
         <v>1991</v>
@@ -24013,10 +24013,10 @@
         <v>566</v>
       </c>
       <c r="B567" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="C567" t="s">
-        <v>1248</v>
+        <v>1247</v>
       </c>
       <c r="D567" t="s">
         <v>72</v>
@@ -24048,10 +24048,10 @@
         <v>567</v>
       </c>
       <c r="B568" t="s">
+        <v>1246</v>
+      </c>
+      <c r="C568" t="s">
         <v>1247</v>
-      </c>
-      <c r="C568" t="s">
-        <v>1248</v>
       </c>
       <c r="D568" t="s">
         <v>72</v>
@@ -24083,13 +24083,13 @@
         <v>568</v>
       </c>
       <c r="B569" t="s">
-        <v>1249</v>
+        <v>1248</v>
       </c>
       <c r="C569" t="s">
         <v>949</v>
       </c>
       <c r="D569" t="s">
-        <v>1250</v>
+        <v>1249</v>
       </c>
       <c r="E569">
         <v>2011</v>

--- a/bds/Biblioteca.xlsx
+++ b/bds/Biblioteca.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\CODE\hermesfar\bds\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49DE6F2A-DAA8-423C-AEC3-67F4C29D8A90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{875FBD1F-8EE2-494F-9832-8C64E3904813}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23964,7 +23964,7 @@
         <v>651</v>
       </c>
       <c r="I565" t="s">
-        <v>14</v>
+        <v>194</v>
       </c>
       <c r="J565" t="s">
         <v>14</v>

--- a/bds/Biblioteca.xlsx
+++ b/bds/Biblioteca.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\CODE\hermesfar\bds\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{875FBD1F-8EE2-494F-9832-8C64E3904813}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9AD07C57-A798-4C8C-875E-45CB48FA9DFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5137" uniqueCount="1251">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5137" uniqueCount="1252">
   <si>
     <t>ID</t>
   </si>
@@ -3786,6 +3786,9 @@
   </si>
   <si>
     <t>El loco de Dios en el fin del mundo</t>
+  </si>
+  <si>
+    <t>Pauli Silberstein</t>
   </si>
 </sst>
 </file>
@@ -13683,7 +13686,7 @@
         <v>14</v>
       </c>
       <c r="K271" t="s">
-        <v>651</v>
+        <v>1251</v>
       </c>
     </row>
     <row r="272" spans="1:11" x14ac:dyDescent="0.3">
@@ -23375,7 +23378,7 @@
         <v>14</v>
       </c>
       <c r="K548" t="s">
-        <v>651</v>
+        <v>1251</v>
       </c>
     </row>
     <row r="549" spans="1:11" x14ac:dyDescent="0.3">
@@ -23725,7 +23728,7 @@
         <v>14</v>
       </c>
       <c r="K558" t="s">
-        <v>651</v>
+        <v>1251</v>
       </c>
     </row>
     <row r="559" spans="1:11" x14ac:dyDescent="0.3">
@@ -24005,7 +24008,7 @@
         <v>14</v>
       </c>
       <c r="K566" t="s">
-        <v>651</v>
+        <v>1251</v>
       </c>
     </row>
     <row r="567" spans="1:11" x14ac:dyDescent="0.3">

--- a/bds/Biblioteca.xlsx
+++ b/bds/Biblioteca.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\CODE\hermesfar\bds\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9AD07C57-A798-4C8C-875E-45CB48FA9DFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DEC152A-E4C5-48F4-BD31-6B0606F3617C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5137" uniqueCount="1252">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5149" uniqueCount="1256">
   <si>
     <t>ID</t>
   </si>
@@ -3789,6 +3789,18 @@
   </si>
   <si>
     <t>Pauli Silberstein</t>
+  </si>
+  <si>
+    <t>Poder político y clases sociales en el Estado capitalista</t>
+  </si>
+  <si>
+    <t>Vicen</t>
+  </si>
+  <si>
+    <t>El sefardí romántico</t>
+  </si>
+  <si>
+    <t>Muñiz-Huberman, A.</t>
   </si>
 </sst>
 </file>
@@ -4189,7 +4201,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K569"/>
+  <dimension ref="A1:K571"/>
   <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="6.44140625" customWidth="1"/>
@@ -23483,7 +23495,7 @@
         <v>14</v>
       </c>
       <c r="K551" t="s">
-        <v>651</v>
+        <v>1253</v>
       </c>
     </row>
     <row r="552" spans="1:11" x14ac:dyDescent="0.3">
@@ -24114,6 +24126,55 @@
       </c>
       <c r="K569" t="s">
         <v>651</v>
+      </c>
+    </row>
+    <row r="570" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A570">
+        <v>569</v>
+      </c>
+      <c r="B570" t="s">
+        <v>1252</v>
+      </c>
+      <c r="C570" t="s">
+        <v>1180</v>
+      </c>
+      <c r="D570" t="s">
+        <v>49</v>
+      </c>
+      <c r="E570">
+        <v>1997</v>
+      </c>
+      <c r="F570" t="s">
+        <v>239</v>
+      </c>
+      <c r="G570" t="s">
+        <v>651</v>
+      </c>
+      <c r="H570" t="s">
+        <v>651</v>
+      </c>
+      <c r="I570" t="s">
+        <v>14</v>
+      </c>
+      <c r="J570" t="s">
+        <v>14</v>
+      </c>
+      <c r="K570" t="s">
+        <v>651</v>
+      </c>
+    </row>
+    <row r="571" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A571">
+        <v>570</v>
+      </c>
+      <c r="B571" t="s">
+        <v>1254</v>
+      </c>
+      <c r="C571" t="s">
+        <v>1255</v>
+      </c>
+      <c r="D571" t="s">
+        <v>683</v>
       </c>
     </row>
   </sheetData>

--- a/bds/Biblioteca.xlsx
+++ b/bds/Biblioteca.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\CODE\hermesfar\bds\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CODE\hermesfar\bds\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DEC152A-E4C5-48F4-BD31-6B0606F3617C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0CB046A3-20FB-41EA-B102-FEB9167ADBE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3788,9 +3788,6 @@
     <t>El loco de Dios en el fin del mundo</t>
   </si>
   <si>
-    <t>Pauli Silberstein</t>
-  </si>
-  <si>
     <t>Poder político y clases sociales en el Estado capitalista</t>
   </si>
   <si>
@@ -3801,6 +3798,9 @@
   </si>
   <si>
     <t>Muñiz-Huberman, A.</t>
+  </si>
+  <si>
+    <t>Lolo</t>
   </si>
 </sst>
 </file>
@@ -4773,7 +4773,7 @@
         <v>14</v>
       </c>
       <c r="K16" t="s">
-        <v>651</v>
+        <v>909</v>
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.3">
@@ -4808,7 +4808,7 @@
         <v>14</v>
       </c>
       <c r="K17" t="s">
-        <v>651</v>
+        <v>909</v>
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.3">
@@ -4843,7 +4843,7 @@
         <v>14</v>
       </c>
       <c r="K18" t="s">
-        <v>651</v>
+        <v>909</v>
       </c>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.3">
@@ -5123,7 +5123,7 @@
         <v>14</v>
       </c>
       <c r="K26" t="s">
-        <v>651</v>
+        <v>909</v>
       </c>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.3">
@@ -6558,7 +6558,7 @@
         <v>14</v>
       </c>
       <c r="K67" t="s">
-        <v>651</v>
+        <v>909</v>
       </c>
     </row>
     <row r="68" spans="1:11" x14ac:dyDescent="0.3">
@@ -6663,7 +6663,7 @@
         <v>14</v>
       </c>
       <c r="K70" t="s">
-        <v>651</v>
+        <v>909</v>
       </c>
     </row>
     <row r="71" spans="1:11" x14ac:dyDescent="0.3">
@@ -13698,7 +13698,7 @@
         <v>14</v>
       </c>
       <c r="K271" t="s">
-        <v>1251</v>
+        <v>651</v>
       </c>
     </row>
     <row r="272" spans="1:11" x14ac:dyDescent="0.3">
@@ -22690,7 +22690,7 @@
         <v>14</v>
       </c>
       <c r="K528" t="s">
-        <v>651</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="529" spans="1:11" x14ac:dyDescent="0.3">
@@ -23390,7 +23390,7 @@
         <v>14</v>
       </c>
       <c r="K548" t="s">
-        <v>1251</v>
+        <v>651</v>
       </c>
     </row>
     <row r="549" spans="1:11" x14ac:dyDescent="0.3">
@@ -23495,7 +23495,7 @@
         <v>14</v>
       </c>
       <c r="K551" t="s">
-        <v>1253</v>
+        <v>1252</v>
       </c>
     </row>
     <row r="552" spans="1:11" x14ac:dyDescent="0.3">
@@ -23740,7 +23740,7 @@
         <v>14</v>
       </c>
       <c r="K558" t="s">
-        <v>1251</v>
+        <v>651</v>
       </c>
     </row>
     <row r="559" spans="1:11" x14ac:dyDescent="0.3">
@@ -24020,7 +24020,7 @@
         <v>14</v>
       </c>
       <c r="K566" t="s">
-        <v>1251</v>
+        <v>651</v>
       </c>
     </row>
     <row r="567" spans="1:11" x14ac:dyDescent="0.3">
@@ -24133,7 +24133,7 @@
         <v>569</v>
       </c>
       <c r="B570" t="s">
-        <v>1252</v>
+        <v>1251</v>
       </c>
       <c r="C570" t="s">
         <v>1180</v>
@@ -24168,10 +24168,10 @@
         <v>570</v>
       </c>
       <c r="B571" t="s">
+        <v>1253</v>
+      </c>
+      <c r="C571" t="s">
         <v>1254</v>
-      </c>
-      <c r="C571" t="s">
-        <v>1255</v>
       </c>
       <c r="D571" t="s">
         <v>683</v>

--- a/bds/Biblioteca.xlsx
+++ b/bds/Biblioteca.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CODE\hermesfar\bds\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0CB046A3-20FB-41EA-B102-FEB9167ADBE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD0C43BD-A3D0-4D5D-8C51-442C2EB4968F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/bds/Biblioteca.xlsx
+++ b/bds/Biblioteca.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\CODE\hermesfar\bds\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CODE\hermesfar\bds\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DEC152A-E4C5-48F4-BD31-6B0606F3617C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD0C43BD-A3D0-4D5D-8C51-442C2EB4968F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3788,9 +3788,6 @@
     <t>El loco de Dios en el fin del mundo</t>
   </si>
   <si>
-    <t>Pauli Silberstein</t>
-  </si>
-  <si>
     <t>Poder político y clases sociales en el Estado capitalista</t>
   </si>
   <si>
@@ -3801,6 +3798,9 @@
   </si>
   <si>
     <t>Muñiz-Huberman, A.</t>
+  </si>
+  <si>
+    <t>Lolo</t>
   </si>
 </sst>
 </file>
@@ -4773,7 +4773,7 @@
         <v>14</v>
       </c>
       <c r="K16" t="s">
-        <v>651</v>
+        <v>909</v>
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.3">
@@ -4808,7 +4808,7 @@
         <v>14</v>
       </c>
       <c r="K17" t="s">
-        <v>651</v>
+        <v>909</v>
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.3">
@@ -4843,7 +4843,7 @@
         <v>14</v>
       </c>
       <c r="K18" t="s">
-        <v>651</v>
+        <v>909</v>
       </c>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.3">
@@ -5123,7 +5123,7 @@
         <v>14</v>
       </c>
       <c r="K26" t="s">
-        <v>651</v>
+        <v>909</v>
       </c>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.3">
@@ -6558,7 +6558,7 @@
         <v>14</v>
       </c>
       <c r="K67" t="s">
-        <v>651</v>
+        <v>909</v>
       </c>
     </row>
     <row r="68" spans="1:11" x14ac:dyDescent="0.3">
@@ -6663,7 +6663,7 @@
         <v>14</v>
       </c>
       <c r="K70" t="s">
-        <v>651</v>
+        <v>909</v>
       </c>
     </row>
     <row r="71" spans="1:11" x14ac:dyDescent="0.3">
@@ -13698,7 +13698,7 @@
         <v>14</v>
       </c>
       <c r="K271" t="s">
-        <v>1251</v>
+        <v>651</v>
       </c>
     </row>
     <row r="272" spans="1:11" x14ac:dyDescent="0.3">
@@ -22690,7 +22690,7 @@
         <v>14</v>
       </c>
       <c r="K528" t="s">
-        <v>651</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="529" spans="1:11" x14ac:dyDescent="0.3">
@@ -23390,7 +23390,7 @@
         <v>14</v>
       </c>
       <c r="K548" t="s">
-        <v>1251</v>
+        <v>651</v>
       </c>
     </row>
     <row r="549" spans="1:11" x14ac:dyDescent="0.3">
@@ -23495,7 +23495,7 @@
         <v>14</v>
       </c>
       <c r="K551" t="s">
-        <v>1253</v>
+        <v>1252</v>
       </c>
     </row>
     <row r="552" spans="1:11" x14ac:dyDescent="0.3">
@@ -23740,7 +23740,7 @@
         <v>14</v>
       </c>
       <c r="K558" t="s">
-        <v>1251</v>
+        <v>651</v>
       </c>
     </row>
     <row r="559" spans="1:11" x14ac:dyDescent="0.3">
@@ -24020,7 +24020,7 @@
         <v>14</v>
       </c>
       <c r="K566" t="s">
-        <v>1251</v>
+        <v>651</v>
       </c>
     </row>
     <row r="567" spans="1:11" x14ac:dyDescent="0.3">
@@ -24133,7 +24133,7 @@
         <v>569</v>
       </c>
       <c r="B570" t="s">
-        <v>1252</v>
+        <v>1251</v>
       </c>
       <c r="C570" t="s">
         <v>1180</v>
@@ -24168,10 +24168,10 @@
         <v>570</v>
       </c>
       <c r="B571" t="s">
+        <v>1253</v>
+      </c>
+      <c r="C571" t="s">
         <v>1254</v>
-      </c>
-      <c r="C571" t="s">
-        <v>1255</v>
       </c>
       <c r="D571" t="s">
         <v>683</v>
